--- a/backend/explanation_cache.xlsx
+++ b/backend/explanation_cache.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1867,6 +1867,328 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>9b4c539948ae24d8c7f3efad2bb6c1665a8d9bae8eec600f286247e1d98acafc</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>spaghetti</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>18.84</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>As a nutrition expert, I'm happy to help you make some healthier adjustments to the classic spaghetti recipe! Here are some suggestions:
+1. Specific substitutions:
+* Use whole wheat spaghetti instead of regular pasta for a fiber and nutrient boost.
+* Choose leaner ground meat alternatives like turkey or chicken breast, or even plant-based options like beans or tofu for a lower saturated fat content.
+* Opt for low-sodium tomato sauce or make your own with fresh vegetables and herbs to reduce salt intake.
+2. Complementary foods:
+* Add some steamed vegetables on the side, such as broccoli or green beans, to increase the nutritional value of the dish.
+* Include a sprinkle of grated Parmesan cheese for added protein and calcium.
+3. Sweetening options:
+* Use a small amount of sugar-free sweetener like stevia or erythritol instead of refined sugar to reduce calories and avoid a spike in blood sugar levels.
+4. Health modifications:
+* Reduce the serving size of the spaghetti and sauce by half to lower the overall carbohydrate and calorie content.
+* Consider using a portion control device, such as a measuring cup or a food scale, to help regulate your intake.
+By making these adjustments, you can enjoy a healthier version of spaghetti that is still delicious and satisfying!</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-06-06 09:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>f357d026fd1c63bd31c495fa14b72c408bbf2d305d5e09cbd80397673b04657b</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>cheesecake</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>23.88</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>As a nutrition expert, I'm happy to help you modify the cheesecake recipe to make it healthier while still maintaining its delicious taste. Here are some suggestions:
+1. Specific substitutions:
+	* Use almond milk or coconut cream instead of heavy cream for a lower calorie and fat content.
+	* Replace granulated sugar with a natural sweetener like honey, maple syrup, or stevia.
+	* Use dark chocolate chips or cocoa nibs instead of semi-sweet chocolate chips for a higher antioxidant content.
+2. Complementary foods:
+	* Add some fresh fruit to the cheesecake batter for natural sweetness and extra fiber. Choose seasonal fruits like berries, citrus, or stone fruits.
+	* Top the cheesecake with a layer of mixed nuts or seeds (e.g., almonds, walnuts, pumpkin seeds) for added crunch and nutritional value.
+3. Sweetening options:
+	* Use a sugar substitute like Erythritol or Xylitol to reduce the calorie content of the cheesecake without sacrificing taste.
+	* Try using a mixture of natural sweeteners, such as honey and maple syrup, for a unique flavor profile.
+4. Health modifications:
+	* Reduce the amount of sugar in the recipe by half and use a sweetener like stevia or erythritol to achieve the desired level of sweetness.
+	* Use a lower-fat version of cream cheese, such as a reduced-fat or non-dairy option, for a healthier cheesecake.
+	* Replace the graham cracker crust with a gluten-free or low-carb alternative to make the cheesecake more accessible to people with dietary restrictions.
+Remember that making significant changes to a recipe can affect its texture and flavor, so it's essential to taste and adjust as you go. By implementing these modifications, you can enjoy a delicious and healthier cheesecake!</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-06-06 09:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>7fdb0b72b68836ed9d1eadf9d59c975766fc975e26ebf01e8b991991f5eac7ea</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Spaghetti Recipe ================ Brief Description: Classic spaghetti dish made with ground beef, t</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>26.02</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>As a nutrition expert, I'm happy to help you modify the Spaghetti Recipe to make it healthier while still maintaining its delicious taste. Here are some suggestions:
+1. Substitutions:
+	* Use leaner ground beef (90% lean) instead of regular ground beef to reduce the saturated fat content.
+	* Replace the onion with a low-carb substitute like shallots or green onions to reduce the carbohydrate content.
+	* Use turkey or chicken sausage instead of ground beef for an even lower saturated fat content.
+2. Complementary foods:
+	* Add some vegetables like cherry tomatoes, bell peppers, or mushrooms to the dish to increase the nutrient density and fiber content.
+	* Use a sugar-free tomato sauce or reduce the amount of tomato sauce used to lower the sugar content.
+3. Sweetening options:
+	* Omit the sugar altogether and use herbs like basil, oregano, or thyme to add flavor to the dish without adding extra sugar.
+	* Use a small amount of stevia or monk fruit sweetener instead of sugar to sweeten the tomato sauce.
+4. Health modifications:
+	* Reduce the cooking time and heat to avoid overcooking the spaghetti, which can make it more prone to overcook and lose its nutrients.
+	* Add some prebiotic fiber like oatmeal or chia seeds to the dish to support gut health.
+Here's an updated version of the Spaghetti Recipe with these modifications:
+Ingredients:
+* 90% lean ground beef (or turkey/chicken sausage)
+* 1 low-carb onion (or shallots/green onions)
+* 2 cups tomato sauce (sugar-free or reduced amount)
+* 1/4 cup oatmeal or chia seeds (prebiotic fiber)
+* Salt and pepper, to taste
+Instructions:
+1. Cook the ground beef in a pan over medium heat until browned, breaking it up into small pieces as it cooks.
+2. Add the chopped onion and cook until softened but not browned.
+3. Add the tomato sauce and cooked spaghetti to the pan and stir to combine.
+4. Cook for an additional 2-3 minutes, or until the spaghetti is heated through.
+5. Stir in the oatmeal or chia seeds and cook for another minute.
+6. Season with salt and pepper to taste, then serve hot.
+This modified Spaghetti Recipe still tastes great but with some healthier modifications to reduce the saturated fat content, increase the fiber content, and support gut health. Enjoy!</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-06-06 10:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1b4c9133da73a711322404314402765ab0d23fd362a167d6f0c65bb215113d94</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>As a nutrition expert, I'm happy to help you modify the orange recipe to suit your dietary needs and preferences. Here are some suggestions:
+1. Specific substitutions:
+	* If you're watching your sugar intake, you could substitute the orange juice with a sugar-free alternative, such as unsweetened almond milk or sparkling water.
+	* For a dairy-free version, use a non-dairy milk like soy milk or coconut milk instead of regular milk.
+	* If you're looking for a lower-carb option, try using a sugar substitute like Stevia or Erythritol to sweeten the orange juice.
+2. Complementary foods:
+	* Pair the orange with some protein-rich foods like nuts, seeds, or hard-boiled eggs to balance out the meal and provide sustained energy.
+	* Add some healthy fats like avocado, olive oil, or chia seeds to the mix for better absorption of vitamins and minerals from the orange.
+3. Sweetening options:
+	* Use a natural sweetener like honey or maple syrup instead of white sugar for a more nuanced flavor and some extra nutrients.
+	* Try using a small amount of brown sugar to balance out the tartness of the orange juice.
+4. Health modifications:
+	* If you're trying to reduce your calorie intake, use a lower-calorie sweetener like Stevia or Erythritol and reduce the amount of orange juice in the recipe accordingly.
+	* For a more nutrient-dense version, try using frozen berries instead of regular orange juice for added fiber, antioxidants, and vitamins.
+By making these modifications, you can create a personalized version of the orange recipe that meets your dietary needs and preferences while still providing a delicious and nutritious snack or meal.</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-06-06 16:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>0d4fc4a78d3706edccafb665a8b2fdd9309e82c78625bb0f2b8e7bb9e1c4d21c</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>17.31</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>As a nutrition expert, I can provide you with some suggestions for modifying the sugar level in the recipe you provided. Here are four options:
+1. Specific Substitutions:
+* Replace 17.3g of sugar with 10-12 g of honey or maple syrup. This will reduce the overall sugar content of the recipe while still providing a sweet flavor.
+* Use 15-17 g of coconut sugar instead of white sugar. Coconut sugar has a lower glycemic index than white sugar, which means it will cause a slower and more gradual increase in blood sugar levels.
+* Replace 17.3g of sugar with 0-2 g of stevia or monk fruit sweetener. These natural sweeteners are low in calories and do not raise blood sugar levels.
+2. Complementary Foods:
+* Add some nuts or seeds to the recipe for added crunch and flavor. Choose options like almonds, walnuts, pumpkin seeds, or sunflower seeds. These foods are high in healthy fats and protein, which can help balance out the sugar content of the recipe.
+* Add some chocolate chips or cocoa powder to the recipe for a rich and indulgent flavor. Chocolate contains antioxidants and can be a good source of fiber and minerals like iron and magnesium.
+3. Sweetening Options:
+* Use a combination of sweeteners to reduce the overall sugar content of the recipe. For example, you could use 10-12 g of honey or maple syrup along with 5-7 g of stevia or monk fruit sweetener. This will provide a balanced sweetness without overloading on refined sugars.
+* Try using a sweetener like xylitol, which has a low glycemic index and does not raise blood sugar levels. Xylitol is found in some fruits and vegetables and can be used as a natural sweetener in baking.
+4. Health Modifications:
+* Reduce the amount of sugar in the recipe by half and replace it with a combination of sweeteners like honey, maple syrup, stevia, or monk fruit sweetener. This will reduce the overall glycemic index of the recipe and make it less likely to cause a spike in blood sugar levels.
+* Add some healthy fats like avocado, nuts, or seeds to the recipe to balance out the carbohydrate content and provide a more sustained energy release.
+Remember, when modifying a recipe it's important to consider the overall nutritional balance of the dish and make sure that any substitutions you make are in line with your dietary goals.</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-06-06 16:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>8286ee4ea8f54f0276bcd4a125de6fd38a58534eebe24df396f05febeee3a91a</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>grapes</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>24.56</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>As a nutrition expert, I'm happy to help you with your query on grapes! Here are some suggestions for substitutions, complementary foods, sweetening options, and health modifications:
+1. Specific Substitutions:
+	* If you're looking for a lower-sugar alternative to grapes, consider trying berries such as blueberries, strawberries, or raspberries. These fruits are naturally sweeter than grapes and have lower sugar levels.
+	* For a higher-protein substitute, try pairing grapes with Greek yogurt or cottage cheese. The protein in these dairy products can help balance out the sugar content of the grapes.
+2. Complementary Foods:
+	* Grapes go well with a variety of foods, including cheese, nuts, and meats. Try pairing grapes with a slice of cheddar cheese or a handful of almonds for a satisfying snack.
+	* If you're looking for a fruit that complements the sweetness of grapes, consider trying pineapple or mango. These fruits have a similar level of sweetness and can balance out the sugar content of grapes.
+3. Sweetening Options:
+	* While grapes are naturally sweet, you may want to reduce the amount of sugar in your recipe. Try using honey or maple syrup as a sweetening agent instead of refined sugar. These options have a lower glycemic index and can provide a more balanced sweetness to your dish.
+	* For a low-sugar substitute, consider using stevia or monk fruit extract. These natural sweeteners are low in calories and don't raise blood sugar levels, making them a great option for those with dietary restrictions.
+4. Health Modifications:
+	* To reduce the sugar content of grapes even further, try using a sugar substitute or reducing the amount of grapes used in your recipe. This can help lower the overall sugar level and make the dish more suitable for a healthy diet.
+	* If you're looking to increase the nutritional value of your grapes, consider adding some nuts or seeds. Almonds or chia seeds can provide a boost of protein and fiber to your snack.
+I hope these suggestions help you modify your recipe to suit your dietary needs!</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-06-06 16:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>c80401b765b44382f7ce3a42bdf96f7cf295e7f350106a1ed0ea35c494f15241</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>grilled salmon with lemon with honey</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>24.06</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>As a nutrition expert, I'm happy to help you modify the grilled salmon with lemon and honey recipe to suit your dietary needs. Here are some suggestions:
+1. Specific Substitutions:
+	* If you're watching your sugar intake, you can substitute the honey with a natural sweetener like stevia or monk fruit sweetener.
+	* For a lower-calorie option, use olive oil instead of regular oil when grilling the salmon.
+	* If you're vegetarian or vegan, you can replace the salmon with tofu or tempeh marinated in lemon juice and herbs.
+2. Complementary Foods:
+	* Pair the grilled salmon with roasted vegetables like asparagus, Brussels sprouts, or sweet potatoes for a well-rounded meal.
+	* Serve the salmon with quinoa or brown rice for a nutritious carb source.
+	* Add some greens like kale or spinach to the dish for an extra boost of nutrients.
+3. Sweetening Options:
+	* If you want to reduce the amount of sugar in the recipe, you can use a sugar substitute like xylitol or erythritol. These sweeteners have a lower glycemic index and don't raise blood sugar levels as much as regular sugar.
+	* You can also try using honey alternatives like manuka honey or acerola cherry juice, which have a lower sugar content than regular honey.
+4. Health Modifications:
+	* If you want to make the recipe even healthier, you can increase the amount of lemon juice and herbs used in the marinade. The acidity from the lemon will help break down the protein and fat in the salmon, making it easier to digest.
+	* You can also add some anti-inflammatory spices like turmeric or ginger to the marinade for added health benefits.
+By making these modifications, you can enjoy a delicious and nutritious grilled salmon dish while still meeting your dietary needs.</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-06-13 16:49</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
